--- a/data/trans_dic/P45C_R1-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R1-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas</t>
+          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,74</t>
+          <t>1,42; 4,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,73</t>
+          <t>0,47; 2,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,59</t>
+          <t>0,59; 3,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,74</t>
+          <t>0,37; 5,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,33</t>
+          <t>0,81; 3,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,87</t>
+          <t>0,87; 3,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,35</t>
+          <t>1,64; 5,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,89</t>
+          <t>0,11; 4,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,39</t>
+          <t>1,4; 3,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,64</t>
+          <t>0,79; 2,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,74</t>
+          <t>1,33; 3,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,85</t>
+          <t>0,54; 3,22</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,28</t>
+          <t>1,17; 3,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,25</t>
+          <t>1,6; 4,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,42</t>
+          <t>0,5; 2,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,55</t>
+          <t>0,8; 5,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,14</t>
+          <t>0,95; 3,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,59</t>
+          <t>0,64; 2,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,32</t>
+          <t>0,5; 2,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,48</t>
+          <t>0,98; 4,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,76</t>
+          <t>1,27; 2,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,03</t>
+          <t>1,4; 3,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,97</t>
+          <t>0,67; 2,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,92</t>
+          <t>1,28; 3,94</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,86</t>
+          <t>0,31; 1,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,45</t>
+          <t>0,14; 1,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,02</t>
+          <t>0,42; 2,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,6</t>
+          <t>1,02; 3,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,16</t>
+          <t>1,52; 4,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,76</t>
+          <t>1,28; 3,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,16</t>
+          <t>0,13; 1,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,35</t>
+          <t>1,15; 3,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,69</t>
+          <t>1,14; 2,59</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,23</t>
+          <t>0,85; 2,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,22</t>
+          <t>0,36; 1,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,99</t>
+          <t>1,31; 2,93</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,01</t>
+          <t>1,19; 4,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,87</t>
+          <t>0,74; 2,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,66</t>
+          <t>0,45; 2,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,03</t>
+          <t>0,78; 3,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,87</t>
+          <t>1,2; 3,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,98</t>
+          <t>0,8; 2,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,67</t>
+          <t>1,09; 2,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,99</t>
+          <t>1,17; 3,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,83</t>
+          <t>1,22; 2,79</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,6</t>
+          <t>0,47; 1,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,27</t>
+          <t>0,8; 2,2</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,1</t>
+          <t>0,51; 2,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,07</t>
+          <t>0,22; 2,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,22; 2,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,86</t>
+          <t>1,14; 3,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,43</t>
+          <t>0,7; 3,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,5</t>
+          <t>0,24; 2,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,33</t>
+          <t>0,24; 2,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,37</t>
+          <t>0,83; 2,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,61</t>
+          <t>0,75; 2,41</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,7</t>
+          <t>0,38; 1,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,81</t>
+          <t>0,36; 1,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,8</t>
+          <t>1,28; 2,71</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,57</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,71</t>
+          <t>0,15; 1,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,97</t>
+          <t>0,17; 2,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,78</t>
+          <t>0,29; 2,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,26</t>
+          <t>0,11; 1,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,87</t>
+          <t>0,28; 1,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,07</t>
+          <t>0,44; 2,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,72</t>
+          <t>0,15; 1,76</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,02</t>
+          <t>0,2; 1,09</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,54</t>
+          <t>0,39; 3,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,53</t>
+          <t>0,13; 1,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,85</t>
+          <t>0,19; 1,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,24</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,36</t>
+          <t>0,12; 1,27</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,76</t>
+          <t>0,11; 0,78</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,19</t>
+          <t>1,28; 2,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,75</t>
+          <t>0,95; 1,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,32</t>
+          <t>0,63; 1,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,16</t>
+          <t>1,15; 2,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,13</t>
+          <t>1,28; 2,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,06</t>
+          <t>1,17; 2,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,55</t>
+          <t>0,8; 1,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,84</t>
+          <t>1,04; 1,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,05</t>
+          <t>1,37; 2,0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,76</t>
+          <t>1,2; 1,79</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,31</t>
+          <t>0,8; 1,33</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,89</t>
+          <t>1,19; 1,86</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas</t>
+          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6720; 23336</t>
+          <t>6981; 23808</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2127; 12293</t>
+          <t>2121; 12028</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2214; 14900</t>
+          <t>2432; 14472</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1429; 18961</t>
+          <t>1491; 22983</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3791; 15504</t>
+          <t>3777; 15302</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3827; 16498</t>
+          <t>3688; 16884</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6340; 21136</t>
+          <t>6493; 20349</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>315; 15328</t>
+          <t>332; 14502</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12713; 32489</t>
+          <t>13399; 32111</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7728; 23108</t>
+          <t>6914; 22239</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10607; 30264</t>
+          <t>10773; 29717</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4322; 27455</t>
+          <t>3871; 22994</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7773; 24093</t>
+          <t>8578; 24781</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11359; 29014</t>
+          <t>10903; 29753</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2951; 14172</t>
+          <t>2923; 14081</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2987; 23505</t>
+          <t>3388; 22276</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5953; 19598</t>
+          <t>5949; 19700</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4666; 15771</t>
+          <t>3904; 16270</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2801; 13068</t>
+          <t>2808; 13116</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5582; 22897</t>
+          <t>5003; 22868</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17233; 37545</t>
+          <t>17210; 37706</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18023; 39061</t>
+          <t>18111; 41121</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7595; 22596</t>
+          <t>7638; 23410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12237; 36623</t>
+          <t>12002; 36866</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2024; 11876</t>
+          <t>1995; 11934</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1280; 9870</t>
+          <t>947; 9383</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2742; 13453</t>
+          <t>2814; 13296</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5441; 19178</t>
+          <t>5440; 20703</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>11331; 28662</t>
+          <t>10477; 29790</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8796; 26492</t>
+          <t>9043; 25581</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>878; 7628</t>
+          <t>882; 8012</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6241; 18179</t>
+          <t>6230; 17637</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14771; 35635</t>
+          <t>15154; 34302</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11141; 30877</t>
+          <t>11811; 31683</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4472; 16087</t>
+          <t>4802; 17230</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14750; 32130</t>
+          <t>14040; 31464</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5653; 20768</t>
+          <t>6151; 21335</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4496; 17444</t>
+          <t>4515; 17513</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7440</t>
+          <t>0; 7629</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3859; 23572</t>
+          <t>4020; 23263</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3931; 15579</t>
+          <t>4011; 16104</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7480; 23658</t>
+          <t>7329; 22546</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4849; 19126</t>
+          <t>5166; 18463</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7488; 18968</t>
+          <t>7718; 19364</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12485; 30888</t>
+          <t>12028; 31481</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14696; 34558</t>
+          <t>14925; 34083</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6135; 20560</t>
+          <t>6047; 20117</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13701; 36289</t>
+          <t>12766; 35191</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1885; 11958</t>
+          <t>1968; 11440</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>932; 8861</t>
+          <t>953; 9000</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 10653</t>
+          <t>1043; 12711</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6900; 21600</t>
+          <t>6410; 20348</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2917; 13876</t>
+          <t>2843; 13711</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1069; 11120</t>
+          <t>1079; 11001</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1166; 11516</t>
+          <t>1161; 10580</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4465; 12999</t>
+          <t>4522; 13642</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6866; 20614</t>
+          <t>5925; 19045</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3283; 14802</t>
+          <t>3326; 15244</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3457; 17472</t>
+          <t>3463; 18048</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13143; 31037</t>
+          <t>14153; 30055</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 7683</t>
+          <t>0; 9098</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>935; 7876</t>
+          <t>0; 7807</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 8478</t>
+          <t>0; 9797</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>666; 6286</t>
+          <t>534; 5755</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>851; 6751</t>
+          <t>590; 7144</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1009; 9695</t>
+          <t>1012; 8846</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 7071</t>
+          <t>0; 7110</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>593; 7647</t>
+          <t>681; 7758</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1872; 11892</t>
+          <t>1755; 11403</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2861; 13568</t>
+          <t>2858; 13398</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1033; 12067</t>
+          <t>1031; 12393</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1652; 9941</t>
+          <t>1958; 10667</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>824; 7424</t>
+          <t>811; 7672</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2153</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5131</t>
+          <t>0; 5226</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>391; 4315</t>
+          <t>374; 4095</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5346</t>
+          <t>0; 5405</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 7599</t>
+          <t>0; 7718</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 5533</t>
+          <t>0; 6388</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3574</t>
+          <t>0; 3341</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1010; 9995</t>
+          <t>1015; 8918</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 7722</t>
+          <t>0; 7516</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>786; 8798</t>
+          <t>773; 8214</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>775; 5367</t>
+          <t>770; 5539</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>41158; 71594</t>
+          <t>41915; 72746</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>32497; 59551</t>
+          <t>32323; 60314</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20462; 44332</t>
+          <t>21110; 45565</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>38688; 74710</t>
+          <t>39776; 77503</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>42023; 71951</t>
+          <t>43297; 73097</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>42517; 72634</t>
+          <t>41378; 72597</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>28480; 54585</t>
+          <t>28262; 53496</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>39338; 67432</t>
+          <t>38216; 67394</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>92764; 135990</t>
+          <t>91197; 133070</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>82646; 121592</t>
+          <t>82768; 124239</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>54591; 89984</t>
+          <t>55294; 91240</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>85001; 134634</t>
+          <t>84783; 132144</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P45C_R1-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R1-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,84</t>
+          <t>1,38; 4,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,67</t>
+          <t>0,46; 2,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,49</t>
+          <t>0,55; 3,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,75</t>
+          <t>0,32; 4,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,29</t>
+          <t>0,81; 3,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,96</t>
+          <t>0,88; 3,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,16</t>
+          <t>1,64; 4,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 4,63</t>
+          <t>0,5; 5,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,35</t>
+          <t>1,3; 3,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,54</t>
+          <t>0,82; 2,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,67</t>
+          <t>1,41; 3,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,22</t>
+          <t>0,81; 3,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,38</t>
+          <t>1,03; 3,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,36</t>
+          <t>1,44; 4,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,41</t>
+          <t>0,52; 2,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,26</t>
+          <t>0,63; 4,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,16</t>
+          <t>0,9; 3,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,67</t>
+          <t>0,67; 2,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,33</t>
+          <t>0,49; 2,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,47</t>
+          <t>1,15; 4,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,78</t>
+          <t>1,25; 2,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,19</t>
+          <t>1,42; 3,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,04</t>
+          <t>0,73; 1,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,94</t>
+          <t>1,23; 3,53</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,87</t>
+          <t>0,45; 1,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,38</t>
+          <t>0,13; 1,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,0</t>
+          <t>0,42; 2,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,89</t>
+          <t>0,9; 3,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,33</t>
+          <t>1,57; 4,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,63</t>
+          <t>1,3; 3,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,22</t>
+          <t>0,13; 1,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,25</t>
+          <t>1,02; 2,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,59</t>
+          <t>1,14; 2,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,29</t>
+          <t>0,88; 2,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,3</t>
+          <t>0,35; 1,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,93</t>
+          <t>1,17; 2,74</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,12</t>
+          <t>1,08; 4,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,88</t>
+          <t>0,71; 2,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,62</t>
+          <t>1,21; 3,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,14</t>
+          <t>0,67; 3,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,68</t>
+          <t>1,34; 3,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,87</t>
+          <t>0,77; 2,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,72</t>
+          <t>1,12; 2,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,05</t>
+          <t>1,12; 3,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,79</t>
+          <t>1,28; 2,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,56</t>
+          <t>0,49; 1,64</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,2</t>
+          <t>1,39; 2,81</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,97</t>
+          <t>0,5; 2,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,11</t>
+          <t>0,22; 2,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,68</t>
+          <t>0,22; 2,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,63</t>
+          <t>1,13; 3,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,39</t>
+          <t>0,74; 3,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,47</t>
+          <t>0,24; 2,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,15</t>
+          <t>0,24; 2,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,49</t>
+          <t>0,85; 2,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,41</t>
+          <t>0,77; 2,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,75</t>
+          <t>0,38; 1,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,87</t>
+          <t>0,36; 1,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,71</t>
+          <t>1,16; 2,67</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,31; 2,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,57</t>
+          <t>0,21; 1,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,08</t>
+          <t>0,25; 2,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,53</t>
+          <t>0,28; 2,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,28</t>
+          <t>0,28; 1,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,8</t>
+          <t>0,28; 2,02</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,04</t>
+          <t>0,43; 2,05</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,76</t>
+          <t>0,15; 1,75</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,09</t>
+          <t>0,38; 1,43</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,66</t>
+          <t>0,39; 3,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,45</t>
+          <t>0,12; 1,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1597,22 +1597,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,65</t>
+          <t>0,2; 1,78</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,27</t>
+          <t>0,12; 1,38</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,78</t>
+          <t>0,11; 0,73</t>
         </is>
       </c>
     </row>
@@ -1644,19 +1644,19 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,23</t>
+          <t>1,27; 2,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,77</t>
+          <t>0,94; 1,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,35</t>
+          <t>0,59; 1,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,24</t>
+          <t>1,25; 2,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,17</t>
+          <t>1,26; 2,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,06</t>
+          <t>1,18; 2,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,52</t>
+          <t>0,79; 1,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,84</t>
+          <t>1,2; 2,04</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,0</t>
+          <t>1,39; 2,05</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,79</t>
+          <t>1,14; 1,75</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,33</t>
+          <t>0,77; 1,29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,86</t>
+          <t>1,32; 1,95</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10693</t>
+          <t>13616</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6981; 23808</t>
+          <t>6816; 24346</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2121; 12028</t>
+          <t>2060; 12512</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2432; 14472</t>
+          <t>2282; 15359</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1491; 22983</t>
+          <t>1303; 19309</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3777; 15302</t>
+          <t>3749; 14625</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3688; 16884</t>
+          <t>3747; 15995</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6493; 20349</t>
+          <t>6459; 19485</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>332; 14502</t>
+          <t>1824; 18279</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13399; 32111</t>
+          <t>12494; 33098</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6914; 22239</t>
+          <t>7183; 23193</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10773; 29717</t>
+          <t>11416; 30034</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3871; 22994</t>
+          <t>6218; 27980</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21632</t>
+          <t>21334</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8578; 24781</t>
+          <t>7593; 23824</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10903; 29753</t>
+          <t>9845; 29589</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2923; 14081</t>
+          <t>3065; 14096</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3388; 22276</t>
+          <t>3015; 21513</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5949; 19700</t>
+          <t>5601; 19788</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3904; 16270</t>
+          <t>4047; 16574</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2808; 13116</t>
+          <t>2774; 12865</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5003; 22868</t>
+          <t>5727; 21584</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17210; 37706</t>
+          <t>16980; 38095</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18111; 41121</t>
+          <t>18348; 41109</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7638; 23410</t>
+          <t>8362; 21509</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12002; 36866</t>
+          <t>11979; 34486</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10860</t>
+          <t>12070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10884</t>
+          <t>11209</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>23279</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1995; 11934</t>
+          <t>2842; 12425</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>947; 9383</t>
+          <t>858; 9570</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2814; 13296</t>
+          <t>2827; 13565</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5440; 20703</t>
+          <t>5564; 20727</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10477; 29790</t>
+          <t>10842; 28823</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9043; 25581</t>
+          <t>9158; 26650</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>882; 8012</t>
+          <t>883; 8137</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6230; 17637</t>
+          <t>6365; 18093</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15154; 34302</t>
+          <t>15161; 35094</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11811; 31683</t>
+          <t>12157; 30771</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4802; 17230</t>
+          <t>4688; 16509</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14040; 31464</t>
+          <t>14440; 33993</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12186</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24481</t>
+          <t>29075</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6151; 21335</t>
+          <t>5605; 21599</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4515; 17513</t>
+          <t>4337; 17510</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 7629</t>
+          <t>0; 7232</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4020; 23263</t>
+          <t>8468; 25807</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4011; 16104</t>
+          <t>3425; 15866</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7329; 22546</t>
+          <t>8180; 22289</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5166; 18463</t>
+          <t>4967; 18350</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7718; 19364</t>
+          <t>8231; 20768</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12028; 31481</t>
+          <t>11503; 31037</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14925; 34083</t>
+          <t>15593; 35638</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6047; 20117</t>
+          <t>6273; 21042</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12766; 35191</t>
+          <t>19891; 40248</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>12745</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8096</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20772</t>
+          <t>21619</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1968; 11440</t>
+          <t>1935; 11031</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>953; 9000</t>
+          <t>943; 9433</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1043; 12711</t>
+          <t>1038; 12017</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6410; 20348</t>
+          <t>6885; 20908</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2843; 13711</t>
+          <t>2977; 13691</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1079; 11001</t>
+          <t>1069; 10555</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1161; 10580</t>
+          <t>1160; 10918</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4522; 13642</t>
+          <t>5184; 15137</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5925; 19045</t>
+          <t>6063; 19891</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3326; 15244</t>
+          <t>3294; 14176</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3463; 18048</t>
+          <t>3504; 18524</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14153; 30055</t>
+          <t>14102; 32485</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2133</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>6174</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 9098</t>
+          <t>0; 8471</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7807</t>
+          <t>952; 7999</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 9797</t>
+          <t>0; 9927</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>534; 5755</t>
+          <t>872; 7369</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>590; 7144</t>
+          <t>852; 8209</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1012; 8846</t>
+          <t>985; 9556</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 7110</t>
+          <t>0; 7083</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>681; 7758</t>
+          <t>1222; 6784</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1755; 11403</t>
+          <t>1788; 12826</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2858; 13398</t>
+          <t>2824; 13442</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1031; 12393</t>
+          <t>1027; 12316</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1958; 10667</t>
+          <t>3191; 12075</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>992</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2537</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>811; 7672</t>
+          <t>824; 7351</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3326,52 +3326,52 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 5226</t>
+          <t>0; 5984</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>374; 4095</t>
+          <t>383; 4492</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5405</t>
+          <t>0; 5164</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 7718</t>
+          <t>0; 7697</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 6388</t>
+          <t>0; 6314</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3341</t>
+          <t>0; 3644</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1015; 8918</t>
+          <t>1066; 9661</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 7516</t>
+          <t>0; 7120</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>773; 8214</t>
+          <t>776; 8930</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>770; 5539</t>
+          <t>845; 5660</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55289</t>
+          <t>60206</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>51696</t>
+          <t>57427</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>106985</t>
+          <t>117633</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>41915; 72746</t>
+          <t>41443; 72470</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>32323; 60314</t>
+          <t>31878; 59707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21110; 45565</t>
+          <t>19928; 43526</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>39776; 77503</t>
+          <t>44235; 80260</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>43297; 73097</t>
+          <t>42484; 72232</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>41378; 72597</t>
+          <t>41573; 72617</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>28262; 53496</t>
+          <t>27888; 52384</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>38216; 67394</t>
+          <t>44932; 75935</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>91197; 133070</t>
+          <t>92113; 136039</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>82768; 124239</t>
+          <t>79250; 120888</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>55294; 91240</t>
+          <t>53130; 88717</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>84783; 132144</t>
+          <t>95811; 141205</t>
         </is>
       </c>
     </row>
